--- a/ml/data/hsn-gst-lookup.xlsx
+++ b/ml/data/hsn-gst-lookup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11859" uniqueCount="4396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11864" uniqueCount="4401">
   <si>
     <t>code</t>
   </si>
@@ -13161,6 +13161,21 @@
   </si>
   <si>
     <t xml:space="preserve">  active        — FALSE hides a chapter/heading you never buy from, without losing coverage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Some rows arrive FALSE already: chapter 77 is reserved and unused, and 78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  rows in CBIC's file look like headings but have no subheadings beneath them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  (mostly subheading text that lost a leading zero and landed in the wrong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  chapter — '3073' reads 'Mussels' but sits in chapter 30, pharmaceuticals).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Setting one back to TRUE will not stick; they are filtered on every rebuild.</t>
   </si>
   <si>
     <t xml:space="preserve">  trade_terms   — semicolon-separated real-world names for this code. THIS IS THE IMPORTANT ONE.</t>
@@ -17395,7 +17410,7 @@
         <v>15</v>
       </c>
       <c r="H119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="s">
         <v>12</v>
@@ -18771,7 +18786,7 @@
         <v>15</v>
       </c>
       <c r="H162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="s">
         <v>12</v>
@@ -19987,7 +20002,7 @@
         <v>15</v>
       </c>
       <c r="H200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="s">
         <v>12</v>
@@ -20019,7 +20034,7 @@
         <v>15</v>
       </c>
       <c r="H201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" t="s">
         <v>12</v>
@@ -20051,7 +20066,7 @@
         <v>15</v>
       </c>
       <c r="H202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" t="s">
         <v>12</v>
@@ -20083,7 +20098,7 @@
         <v>15</v>
       </c>
       <c r="H203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I203" t="s">
         <v>12</v>
@@ -20115,7 +20130,7 @@
         <v>15</v>
       </c>
       <c r="H204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" t="s">
         <v>12</v>
@@ -20147,7 +20162,7 @@
         <v>15</v>
       </c>
       <c r="H205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" t="s">
         <v>12</v>
@@ -20179,7 +20194,7 @@
         <v>15</v>
       </c>
       <c r="H206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" t="s">
         <v>12</v>
@@ -20211,7 +20226,7 @@
         <v>15</v>
       </c>
       <c r="H207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" t="s">
         <v>12</v>
@@ -20243,7 +20258,7 @@
         <v>15</v>
       </c>
       <c r="H208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I208" t="s">
         <v>12</v>
@@ -20275,7 +20290,7 @@
         <v>15</v>
       </c>
       <c r="H209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" t="s">
         <v>12</v>
@@ -20531,7 +20546,7 @@
         <v>15</v>
       </c>
       <c r="H217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" t="s">
         <v>12</v>
@@ -26899,7 +26914,7 @@
         <v>15</v>
       </c>
       <c r="H416" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I416" t="s">
         <v>12</v>
@@ -26931,7 +26946,7 @@
         <v>15</v>
       </c>
       <c r="H417" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I417" t="s">
         <v>12</v>
@@ -26963,7 +26978,7 @@
         <v>15</v>
       </c>
       <c r="H418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I418" t="s">
         <v>12</v>
@@ -26995,7 +27010,7 @@
         <v>15</v>
       </c>
       <c r="H419" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I419" t="s">
         <v>12</v>
@@ -27027,7 +27042,7 @@
         <v>15</v>
       </c>
       <c r="H420" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I420" t="s">
         <v>12</v>
@@ -27059,7 +27074,7 @@
         <v>15</v>
       </c>
       <c r="H421" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I421" t="s">
         <v>12</v>
@@ -27091,7 +27106,7 @@
         <v>15</v>
       </c>
       <c r="H422" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I422" t="s">
         <v>12</v>
@@ -27123,7 +27138,7 @@
         <v>15</v>
       </c>
       <c r="H423" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I423" t="s">
         <v>12</v>
@@ -27155,7 +27170,7 @@
         <v>15</v>
       </c>
       <c r="H424" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I424" t="s">
         <v>12</v>
@@ -27187,7 +27202,7 @@
         <v>15</v>
       </c>
       <c r="H425" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I425" t="s">
         <v>12</v>
@@ -27219,7 +27234,7 @@
         <v>15</v>
       </c>
       <c r="H426" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I426" t="s">
         <v>12</v>
@@ -27251,7 +27266,7 @@
         <v>15</v>
       </c>
       <c r="H427" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I427" t="s">
         <v>12</v>
@@ -27283,7 +27298,7 @@
         <v>15</v>
       </c>
       <c r="H428" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I428" t="s">
         <v>12</v>
@@ -27315,7 +27330,7 @@
         <v>15</v>
       </c>
       <c r="H429" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I429" t="s">
         <v>12</v>
@@ -27347,7 +27362,7 @@
         <v>15</v>
       </c>
       <c r="H430" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I430" t="s">
         <v>12</v>
@@ -27379,7 +27394,7 @@
         <v>15</v>
       </c>
       <c r="H431" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I431" t="s">
         <v>12</v>
@@ -27411,7 +27426,7 @@
         <v>15</v>
       </c>
       <c r="H432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I432" t="s">
         <v>12</v>
@@ -27475,7 +27490,7 @@
         <v>15</v>
       </c>
       <c r="H434" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I434" t="s">
         <v>12</v>
@@ -27507,7 +27522,7 @@
         <v>15</v>
       </c>
       <c r="H435" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I435" t="s">
         <v>12</v>
@@ -27539,7 +27554,7 @@
         <v>15</v>
       </c>
       <c r="H436" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I436" t="s">
         <v>12</v>
@@ -27571,7 +27586,7 @@
         <v>15</v>
       </c>
       <c r="H437" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I437" t="s">
         <v>12</v>
@@ -27603,7 +27618,7 @@
         <v>15</v>
       </c>
       <c r="H438" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I438" t="s">
         <v>12</v>
@@ -27635,7 +27650,7 @@
         <v>15</v>
       </c>
       <c r="H439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I439" t="s">
         <v>12</v>
@@ -27667,7 +27682,7 @@
         <v>15</v>
       </c>
       <c r="H440" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I440" t="s">
         <v>12</v>
@@ -27699,7 +27714,7 @@
         <v>15</v>
       </c>
       <c r="H441" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I441" t="s">
         <v>12</v>
@@ -27731,7 +27746,7 @@
         <v>15</v>
       </c>
       <c r="H442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I442" t="s">
         <v>12</v>
@@ -27763,7 +27778,7 @@
         <v>15</v>
       </c>
       <c r="H443" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I443" t="s">
         <v>12</v>
@@ -27827,7 +27842,7 @@
         <v>15</v>
       </c>
       <c r="H445" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I445" t="s">
         <v>12</v>
@@ -27891,7 +27906,7 @@
         <v>15</v>
       </c>
       <c r="H447" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I447" t="s">
         <v>12</v>
@@ -27923,7 +27938,7 @@
         <v>15</v>
       </c>
       <c r="H448" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I448" t="s">
         <v>12</v>
@@ -27955,7 +27970,7 @@
         <v>15</v>
       </c>
       <c r="H449" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I449" t="s">
         <v>12</v>
@@ -27987,7 +28002,7 @@
         <v>15</v>
       </c>
       <c r="H450" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I450" t="s">
         <v>12</v>
@@ -28051,7 +28066,7 @@
         <v>15</v>
       </c>
       <c r="H452" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I452" t="s">
         <v>12</v>
@@ -28083,7 +28098,7 @@
         <v>15</v>
       </c>
       <c r="H453" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I453" t="s">
         <v>12</v>
@@ -28115,7 +28130,7 @@
         <v>15</v>
       </c>
       <c r="H454" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I454" t="s">
         <v>12</v>
@@ -28147,7 +28162,7 @@
         <v>15</v>
       </c>
       <c r="H455" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I455" t="s">
         <v>12</v>
@@ -32467,7 +32482,7 @@
         <v>15</v>
       </c>
       <c r="H590" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I590" t="s">
         <v>12</v>
@@ -32499,7 +32514,7 @@
         <v>15</v>
       </c>
       <c r="H591" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I591" t="s">
         <v>12</v>
@@ -32531,7 +32546,7 @@
         <v>15</v>
       </c>
       <c r="H592" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I592" t="s">
         <v>12</v>
@@ -35987,7 +36002,7 @@
         <v>15</v>
       </c>
       <c r="H700" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I700" t="s">
         <v>12</v>
@@ -39571,7 +39586,7 @@
         <v>15</v>
       </c>
       <c r="H812" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I812" t="s">
         <v>12</v>
@@ -39603,7 +39618,7 @@
         <v>15</v>
       </c>
       <c r="H813" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I813" t="s">
         <v>12</v>
@@ -41907,7 +41922,7 @@
         <v>15</v>
       </c>
       <c r="H885" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I885" t="s">
         <v>12</v>
@@ -41939,7 +41954,7 @@
         <v>15</v>
       </c>
       <c r="H886" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I886" t="s">
         <v>12</v>
@@ -41971,7 +41986,7 @@
         <v>15</v>
       </c>
       <c r="H887" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I887" t="s">
         <v>12</v>
@@ -42003,7 +42018,7 @@
         <v>15</v>
       </c>
       <c r="H888" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I888" t="s">
         <v>12</v>
@@ -42035,7 +42050,7 @@
         <v>15</v>
       </c>
       <c r="H889" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I889" t="s">
         <v>12</v>
@@ -42067,7 +42082,7 @@
         <v>15</v>
       </c>
       <c r="H890" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I890" t="s">
         <v>12</v>
@@ -42099,7 +42114,7 @@
         <v>15</v>
       </c>
       <c r="H891" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I891" t="s">
         <v>12</v>
@@ -42131,7 +42146,7 @@
         <v>15</v>
       </c>
       <c r="H892" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I892" t="s">
         <v>12</v>
@@ -42163,7 +42178,7 @@
         <v>15</v>
       </c>
       <c r="H893" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I893" t="s">
         <v>12</v>
@@ -43859,7 +43874,7 @@
         <v>15</v>
       </c>
       <c r="H946" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I946" t="s">
         <v>12</v>
@@ -43891,7 +43906,7 @@
         <v>15</v>
       </c>
       <c r="H947" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I947" t="s">
         <v>12</v>
@@ -43923,7 +43938,7 @@
         <v>15</v>
       </c>
       <c r="H948" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I948" t="s">
         <v>12</v>
@@ -44563,7 +44578,7 @@
         <v>15</v>
       </c>
       <c r="H968" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I968" t="s">
         <v>12</v>
@@ -44595,7 +44610,7 @@
         <v>15</v>
       </c>
       <c r="H969" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I969" t="s">
         <v>12</v>
@@ -48691,7 +48706,7 @@
         <v>15</v>
       </c>
       <c r="H1097" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1097" t="s">
         <v>12</v>
@@ -48723,7 +48738,7 @@
         <v>15</v>
       </c>
       <c r="H1098" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1098" t="s">
         <v>12</v>
@@ -48755,7 +48770,7 @@
         <v>15</v>
       </c>
       <c r="H1099" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1099" t="s">
         <v>12</v>
@@ -48787,7 +48802,7 @@
         <v>15</v>
       </c>
       <c r="H1100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1100" t="s">
         <v>12</v>
@@ -48819,7 +48834,7 @@
         <v>15</v>
       </c>
       <c r="H1101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1101" t="s">
         <v>12</v>
@@ -48851,7 +48866,7 @@
         <v>15</v>
       </c>
       <c r="H1102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1102" t="s">
         <v>12</v>
@@ -48883,7 +48898,7 @@
         <v>15</v>
       </c>
       <c r="H1103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1103" t="s">
         <v>12</v>
@@ -50259,7 +50274,7 @@
         <v>15</v>
       </c>
       <c r="H1146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1146" t="s">
         <v>12</v>
@@ -57203,7 +57218,7 @@
         <v>15</v>
       </c>
       <c r="H1363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1363" t="s">
         <v>12</v>
@@ -60933,7 +60948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -60996,32 +61011,32 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4384</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>4385</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4386</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4387</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4388</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -61031,37 +61046,62 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>4390</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4391</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>4392</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>4393</v>
+        <v>4394</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>4394</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4400</v>
       </c>
     </row>
   </sheetData>
